--- a/AAII_Financials/Quarterly/WMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WMT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>WMT</t>
   </si>
@@ -656,503 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43039</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42947</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42766</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>187937000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>177751000</v>
+      </c>
+      <c r="F8" s="3">
         <v>190656000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>179496000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>177402000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>165609000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>180554000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>169588000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>169335000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>161508000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>173388000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>160804000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>161632000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>152301000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>164048000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>152813000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>152859000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>141569000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>152871000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>140525000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>141048000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>138310000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>152079000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>134708000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>137742000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>134622000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>141671000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>127991000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>130377000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>123925000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>138793000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>124894000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>128028000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>122690000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>136267000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>123179000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>123355000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>117542000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>130936000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>118179000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>141704000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>133058000</v>
+      </c>
+      <c r="F9" s="3">
         <v>143615000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>134706000</v>
       </c>
-      <c r="F9" s="3">
-        <v>132671000</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>132771000</v>
+      </c>
+      <c r="I9" s="3">
         <v>124303000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>136172000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>127340000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>126810000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>121431000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>131825000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>121183000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>121850000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>115284000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>125423000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>115613000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>115838000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>106847000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>115522000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>105023000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>105183000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>103272000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>115261000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>100339000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>102689000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>102026000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>107748000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>95900000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>97923000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>93034000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>104907000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>93116000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>95571000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>91707000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>102640000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>91547000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>91521000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>87688000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>97743000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>87484000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>46233000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>44693000</v>
+      </c>
+      <c r="F10" s="3">
         <v>47041000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>44790000</v>
       </c>
-      <c r="F10" s="3">
-        <v>44731000</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>44631000</v>
+      </c>
+      <c r="I10" s="3">
         <v>41306000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>44382000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>42248000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>42525000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>40077000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>41563000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>39621000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>39782000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>37017000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>38625000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>37200000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>37021000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>34722000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>37349000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>35502000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>35865000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>35038000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>36818000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>34369000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>35053000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>32596000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>33923000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>32091000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>32454000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>30891000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>33886000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>31778000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>32457000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>30983000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>33627000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>31632000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>31834000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>29854000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>33193000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>30695000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1218,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1313,8 +1339,14 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,172 +1464,184 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1700000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-260000</v>
+      </c>
+      <c r="F14" s="3">
         <v>2023000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>2100000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
+        <v>-2308000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>551000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>446000</v>
+      </c>
+      <c r="K14" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
+        <v>-639000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>-228000</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
+        <v>-3200000</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>3062000</v>
+      </c>
+      <c r="R14" s="3">
+        <v>800000</v>
+      </c>
+      <c r="S14" s="3">
+        <v>3300000</v>
+      </c>
+      <c r="T14" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>500000</v>
       </c>
-      <c r="G14" s="3">
-        <v>551000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>446000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>100000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-639000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>-228000</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
-        <v>-3200000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>3062000</v>
-      </c>
-      <c r="P14" s="3">
-        <v>800000</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>3300000</v>
-      </c>
-      <c r="R14" s="3">
-        <v>-200000</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
-        <v>500000</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>2610000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>1200000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>1100000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>8400000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>1600000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>1900000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>900000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>4800000</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>1004000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>1344000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>788000</v>
-      </c>
-      <c r="AM14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3925000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3821000</v>
+      </c>
+      <c r="F15" s="3">
         <v>3741000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>3606000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>3487000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>3369000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>3374000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>3260000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>3211000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>3128000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>3117000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>2986000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>2905000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>2845000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1670,8 +1714,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1760,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>181454000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>170258000</v>
+      </c>
+      <c r="F17" s="3">
         <v>181948000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>172800000</v>
       </c>
-      <c r="F17" s="3">
-        <v>169616000</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>169716000</v>
+      </c>
+      <c r="I17" s="3">
         <v>158474000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>172695000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>162880000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>161395000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>154667000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>166134000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>154602000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>154316000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>146061000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>158487000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>150118000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>145805000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>136251000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>146984000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>137143000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>133694000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>132201000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>153992000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>129930000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>131683000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>129398000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>136349000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>123273000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>124794000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>118980000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>132726000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>119908000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>127078000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>117536000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>132804000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>119759000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>118174000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>112305000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>124731000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>113060000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6483000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>7493000</v>
+      </c>
+      <c r="F18" s="3">
         <v>8708000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>6696000</v>
       </c>
-      <c r="F18" s="3">
-        <v>7786000</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>7686000</v>
+      </c>
+      <c r="I18" s="3">
         <v>7135000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>7859000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>6708000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>7940000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>6841000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>7254000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>6202000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>7316000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>6240000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>5561000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>2695000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>7054000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>5318000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>5887000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>3382000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>7354000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>6109000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1913000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>4778000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>6059000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>5224000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>5322000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>4718000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>5583000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>4945000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>6067000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>4986000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>950000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>5154000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>3463000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>3420000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>5181000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>5237000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>6205000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>5119000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,603 +2055,635 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="F20" s="3">
         <v>94000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-4181000</v>
       </c>
-      <c r="F20" s="3">
-        <v>-2708000</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>46000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-152000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>32000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1162000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-155000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-585000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>4750000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-705000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-67000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>3951000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-3542000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>69000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1962000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-678000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>1251000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-916000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1699000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1844000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>2878000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>3245000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>764000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>1003000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>288000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>885000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>266000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-1817000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>2000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>37000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>42000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>38000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>35000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>30000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10408000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>11329000</v>
+      </c>
+      <c r="F21" s="3">
         <v>12355000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>14483000</v>
       </c>
-      <c r="F21" s="3">
-        <v>13981000</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>11173000</v>
+      </c>
+      <c r="I21" s="3">
         <v>10458000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>11385000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>9936000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>9989000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>10124000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>10956000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4438000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>10926000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>9152000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>12323000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1908000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>9822000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>6036000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>7915000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>7283000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>9079000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>7071000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>2750000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>10427000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>12075000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>8779000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>9153000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>7729000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>8276000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>8544000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>9064000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>5784000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>3606000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>6030000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>6202000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>6120000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>7837000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>7823000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>8941000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>7612000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>699000</v>
+      </c>
+      <c r="F22" s="3">
         <v>709000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>684000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>769000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>637000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>717000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>618000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>679000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>714000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>695000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>682000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>642000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>664000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>610000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>584000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>479000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>455000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>427000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>486000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>515000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>566000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>524000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>541000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>658000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>592000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>652000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>633000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>641000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>673000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>669000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>593000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>554000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>530000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>536000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>583000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>613000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>598000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>585000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AQ22" s="3">
         <v>609000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8012000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>7148000</v>
+      </c>
+      <c r="F23" s="3">
         <v>5970000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>8186000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>9319000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>5994000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>6963000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>6098000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>6213000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>7035000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>7518000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>915000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>10727000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2688000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>8902000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1431000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>6644000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>2901000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>4782000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>4147000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>5923000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>3844000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-593000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>7115000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>8646000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>5396000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>5673000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>4373000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>4913000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>5157000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>5664000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>2576000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>398000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>2822000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>2964000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>2879000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>4606000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>4674000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>5650000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>4534000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1483000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1658000</v>
+      </c>
+      <c r="F24" s="3">
         <v>1578000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>2098000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>2168000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1355000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1538000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1384000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1502000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1728000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1840000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>272000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>2674000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>792000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>3093000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>336000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1497000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>798000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1149000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1015000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>1559000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1033000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1415000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>1914000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>2207000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>1322000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>1379000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>1052000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>1233000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>1251000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>1343000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>806000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>1002000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>688000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>801000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>975000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>1502000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>1522000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>1664000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>1332000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2801,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6529000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5490000</v>
+      </c>
+      <c r="F26" s="3">
         <v>4392000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>6088000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>7151000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>4639000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>5425000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>4714000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>4711000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>5307000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>5678000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>643000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>8053000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1896000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>5809000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1767000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>5147000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2103000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>3633000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>3132000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>4364000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>2811000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2008000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>5201000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>6439000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>4074000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>4294000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>3321000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>3680000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>3906000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>4321000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>1770000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-604000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>2134000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>2163000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>1904000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>3104000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>3152000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>3986000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>3202000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6366000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>5330000</v>
+      </c>
+      <c r="F27" s="3">
         <v>4237000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>6143000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>7026000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>4487000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>5254000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>4577000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>4501000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>5104000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>5494000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>453000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>7891000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1673000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>6275000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1798000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>5149000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2054000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>3562000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>3105000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>4276000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>2730000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-2091000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>5135000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>6476000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>3990000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>4141000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>3288000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>3610000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>3842000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>4195000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>1663000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-738000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>1992000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>1975000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>1749000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>2899000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>3039000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>3757000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>3034000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3176,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3133,56 +3253,62 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-508000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AI29" s="3">
         <v>47000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AJ29" s="3">
         <v>-123000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AK29" s="3">
         <v>142000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AL29" s="3">
         <v>200000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3426,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,246 +3551,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-94000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>4181000</v>
       </c>
-      <c r="F32" s="3">
-        <v>2708000</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-46000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>152000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-32000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1162000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>155000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>585000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-4750000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>705000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>67000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-3951000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>3542000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-69000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1962000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>678000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-1251000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>916000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1699000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1844000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-2878000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-3245000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-764000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-1003000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-288000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>29000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-885000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-266000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>1817000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>1802000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-37000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-42000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-38000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-35000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>-24000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6366000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>5330000</v>
+      </c>
+      <c r="F33" s="3">
         <v>4237000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>6143000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>7026000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>4487000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>5254000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>4577000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>4501000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>5104000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>5494000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>453000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>7891000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1673000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>6275000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1798000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>5149000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2054000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>3562000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>3105000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>4276000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>2730000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-2091000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>5135000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>6476000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>3990000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>4141000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>3288000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>3610000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>3842000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>3687000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>1710000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-861000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>2134000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>2175000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>1749000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>2899000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>3039000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>3757000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>3034000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3926,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6366000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>5330000</v>
+      </c>
+      <c r="F35" s="3">
         <v>4237000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>6143000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>7026000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>4487000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>5254000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>4577000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>4501000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>5104000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>5494000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>453000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>7891000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1673000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>6275000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1798000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>5149000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2054000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>3562000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>3105000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>4276000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>2730000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-2091000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>5135000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>6476000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>3990000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>4141000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>3288000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>3610000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>3842000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>3687000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>1710000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-861000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>2134000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>2175000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>1749000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>2899000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>3039000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>3757000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>3034000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43039</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42947</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42766</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4230,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,127 +4275,135 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11529000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10729000</v>
+      </c>
+      <c r="F41" s="3">
         <v>10727000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10582000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9431000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9311000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9037000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10049000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8811000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9405000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>9867000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>12154000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>13888000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>10575000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>8625000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>11587000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>13923000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>11817000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>14760000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>16111000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>22831000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>22846000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>17741000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>14325000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>16906000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>14930000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>9465000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>8606000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>9283000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>9255000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>7722000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>9174000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>15840000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>7885000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>6456000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>7026000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>6469000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>6545000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>6602000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>5939000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4343,246 +4521,264 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11075000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10662000</v>
+      </c>
+      <c r="F43" s="3">
         <v>11172000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>12115000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>10518000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>9686000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>9975000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>10039000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>8650000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>9075000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>8796000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>8625000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>7891000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>7647000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>7933000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>8218000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>7522000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>7674000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>8280000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>7349000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>6103000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>5797000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>6516000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>5770000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>5111000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>5029000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>6284000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>5612000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>5382000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>5342000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>6283000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>5785000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>5002000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>4568000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>5614000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>5865000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>5395000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>5252000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>5835000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>5344000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>61600000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>62570000</v>
+      </c>
+      <c r="F44" s="3">
         <v>58851000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>65354000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>57729000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>57467000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>56435000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>63302000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>55611000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>55382000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>54892000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>63951000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>56722000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>56932000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>56576000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>64706000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>59921000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>61229000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>56511000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>57484000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>47754000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>46383000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>44949000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>51842000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>41084000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>41217000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>44435000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>51546000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>44134000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>44751000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>44269000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>50380000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>41985000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>43303000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>43783000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>50147000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>43442000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>43361000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>43046000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>49822000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4622,250 +4818,262 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>2521000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>3169000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2798000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>2500000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1519000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2020000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1555000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1565000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>20861000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1665000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1895000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>2152000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1622000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>2148000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>2572000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>2391000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>3623000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>4107000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>3543000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>3486000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>3811000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>2330000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>1457000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>2178000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>2206000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>2296000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>88703000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>88394000</v>
+      </c>
+      <c r="F46" s="3">
         <v>84874000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>92920000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>82033000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>80253000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>79458000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>86938000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>76510000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>77152000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>76877000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>88391000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>82032000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>78511000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>75655000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>87680000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>84164000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>83220000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>81070000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>82964000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>78243000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>76591000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>90067000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>73602000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>64996000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>63328000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>61806000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>67912000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>61371000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>61739000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>61897000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>69446000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>66370000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>59242000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>59664000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>65368000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>56763000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>57336000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>57689000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>63401000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4867000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6009000</v>
+      </c>
+      <c r="F47" s="3">
         <v>5675000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>6711000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>4563000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2392000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>4222000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2966000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>6684000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>7820000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>8449000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>6468000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>10705000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2191000</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -4938,246 +5146,264 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>164310000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>159042000</v>
+      </c>
+      <c r="F48" s="3">
         <v>156956000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>150840000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>145557000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>140884000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>139704000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>136526000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>133738000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>131345000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>130338000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>126824000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>123995000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>121138000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>119234000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>115544000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>114392000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>113217000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>112624000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>110331000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>109598000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>108625000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>109848000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>124289000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>122894000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>123378000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>127049000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>125425000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>125862000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>125241000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>111395000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>111349000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>111017000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>114800000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>114818000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>115299000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>115353000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>114169000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>114178000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>115088000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28260000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>28152000</v>
+      </c>
+      <c r="F49" s="3">
         <v>33035000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>28722000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>29060000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>28866000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>33292000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>27942000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>27930000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>27999000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>32213000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>28015000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>28268000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>28306000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>28174000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>28137000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>28664000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>29438000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>29014000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>28923000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>29159000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>28872000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>28983000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>30236000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>29542000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>29416000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>31073000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>30716000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>31454000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>31416000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>31181000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>31044000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>17840000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>18850000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>18242000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>18204000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>18037000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>17575000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>17037000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>17792000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5521,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5646,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7774000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>8010000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2237000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>9462000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>9624000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>9977000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>2399000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>9027000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>9578000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>9738000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2859000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>9476000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>10121000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>14907000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>20134000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>16295000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>19979000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>20267000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>22152000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>22633000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>21552000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>22493000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>23598000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>22736000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>19950000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>16770000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>16567000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>15777000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>16174000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>16148000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>14822000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>14744000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>10835000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>12035000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>11798000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>10543000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>11413000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>10638000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>9921000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>10576000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5896,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>293914000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>289607000</v>
+      </c>
+      <c r="F54" s="3">
         <v>284668000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>288655000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>270837000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>262372000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>260823000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>263399000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>254440000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>254054000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>252399000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>259174000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>255121000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>245053000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>243197000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>247656000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>247199000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>246142000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>244860000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>244851000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>238552000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>236581000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>252496000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>250863000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>237382000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>232892000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>236495000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>239830000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>234861000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>234544000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>219295000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>226583000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>206062000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>204927000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>204522000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>209414000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>201566000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>199718000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>198825000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>206857000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +6070,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,722 +6115,760 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>64318000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>62876000</v>
+      </c>
+      <c r="F57" s="3">
         <v>63061000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>67156000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>60086000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>57700000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>58666000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>62863000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>56716000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>56071000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>56812000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>61049000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>56576000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>54268000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>53742000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>57263000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>54191000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>52926000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>55261000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>57156000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>49601000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>48151000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>49141000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>54152000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>46326000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>44096000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>46973000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>49750000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>45871000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>45110000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>47060000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>49729000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>43128000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>44612000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>46092000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>47587000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>42389000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>41367000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>41433000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>42990000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16543000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>17082000</v>
+      </c>
+      <c r="F58" s="3">
         <v>12625000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>14358000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>10256000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>12010000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7965000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>9121000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6969000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>9648000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>6537000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>14910000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>9568000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>7783000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>5130000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>12818000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>16484000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>15523000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>3724000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2530000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>2789000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>4369000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3830000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>5172000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>6459000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>10554000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>6448000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>9487000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>8516000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>6727000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>7830000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>11095000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>2228000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>10038000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>9662000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>9021000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>7174000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>6472000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>3920000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AQ58" s="3">
         <v>7897000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4695000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7095000</v>
+      </c>
+      <c r="F59" s="3">
         <v>3537000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2697000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4403000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>7125000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3363000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2457000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3919000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>6289000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2971000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5439000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>6637000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>8727000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>33326000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>31327000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>29224000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>28081000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>28394000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>27934000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>28732000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>28321000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>39674000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>28797000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>29172000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>27997000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>24369000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>24547000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>25896000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>28051000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>22587000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>24927000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>26327000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>26107000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>22767000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>23827000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>23248000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>26354000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>21575000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>23243000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>115630000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>114583000</v>
+      </c>
+      <c r="F60" s="3">
         <v>107469000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>115732000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>103566000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>102920000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>96584000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>102558000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>95260000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>96100000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>92415000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>104230000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>99220000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>95505000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>92198000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>101408000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>99899000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>96530000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>87379000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>87620000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>81122000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>80841000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>92645000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>88121000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>81957000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>82647000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>77790000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>83784000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>80283000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>79888000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>77477000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>85751000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>71683000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>80757000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>78521000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>80435000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>72811000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>74193000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>66928000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>74130000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58549000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>58463000</v>
+      </c>
+      <c r="F61" s="3">
         <v>55801000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>54066000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>56303000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>56683000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>54148000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>54457000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>56177000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>56890000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>56740000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>57070000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>57293000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>58275000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>39492000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>38447000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>34221000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>36583000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>39107000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>40486000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>43533000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>44075000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>45041000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>45599000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>45632000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>47480000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>48021000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>45150000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>44612000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>47441000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>46340000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>46161000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>47732000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>32330000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>32784000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>36483000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>36025000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>40025000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>42018000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>42108000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>5969000</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>8</v>
+      <c r="F62" s="3">
+        <v>5969000</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H62" s="3">
-        <v>5380000</v>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
+      <c r="J62" s="3">
+        <v>5380000</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>5425000</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
+      <c r="N62" s="3">
+        <v>5425000</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3">
         <v>27516000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>27418000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>27232000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>27169000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>26483000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>25988000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>26770000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>27073000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>27279000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>29639000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>28596000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>28655000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>29132000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>32589000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>32835000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>32305000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>15844000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>15202000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>12835000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>13516000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>12395000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>13590000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>13684000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>9386000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>9344000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>10144000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6986,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +7111,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7236,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>189115000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>188632000</v>
+      </c>
+      <c r="F66" s="3">
         <v>178488000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>186143000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>173980000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>171724000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>163131000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>168934000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>163668000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>165764000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>161828000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>173363000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>169562000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>165588000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>166504000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>175403000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>169630000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>169246000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>161607000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>162577000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>158023000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>158246000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>171571000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>169432000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>162072000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>164652000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>161826000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>168181000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>164534000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>166339000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>146799000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>154587000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>134877000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>129375000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>126653000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>133269000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>125177000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>126027000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>121027000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>129164000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7410,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7531,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7656,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7781,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7906,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>103601000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>100241000</v>
+      </c>
+      <c r="F72" s="3">
         <v>104774000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>101558000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>96328000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>90849000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>98313000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>94435000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>90788000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>87230000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>89814000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>85831000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>85470000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>78035000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>83135000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>77946000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>82519000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>80532000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>86904000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>85674000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>84572000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>82577000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>88763000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>92279000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>87614000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>81141000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>83943000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>80656000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>78432000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>76276000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>80785000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>80287000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>80810000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>82982000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>85107000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>84480000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>84838000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>84120000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>89354000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>87636000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +8156,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8281,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8406,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>98238000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>94330000</v>
+      </c>
+      <c r="F76" s="3">
         <v>99617000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>96094000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>90110000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>83793000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>91013000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>88108000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>84423000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>81293000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>83861000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>79456000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>79556000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>72405000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>76693000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>72253000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>77569000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>76896000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>83253000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>82274000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>80529000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>78335000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>80925000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>81431000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>75310000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>68240000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>74669000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>71649000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>70327000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>68205000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>72496000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>71996000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>71185000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>75552000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>77869000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>76145000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>76389000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>73691000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>77798000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>77693000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8656,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43039</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42947</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42766</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6366000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>5330000</v>
+      </c>
+      <c r="F81" s="3">
         <v>4237000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>6143000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>7026000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>4487000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>5254000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>4577000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>4501000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>5104000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>5494000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>453000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>7891000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1673000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>6275000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1798000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>5149000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2054000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>3562000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>3105000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>4276000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>2730000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-2091000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>5135000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>6476000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>3990000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>4141000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>3288000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>3610000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>3842000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>3687000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>1710000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-861000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>2134000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>2175000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>1749000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>2899000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>3039000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>3757000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>3034000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8960,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3487000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3369000</v>
+      </c>
+      <c r="F83" s="3">
         <v>3374000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>3260000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>3211000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>3128000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>3117000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>2986000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>2905000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2845000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>2811000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>2755000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>2699000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>2680000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>2811000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>2755000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>2699000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>2680000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>2706000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>2650000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>2641000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>2661000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>2819000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>2771000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>2771000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>2791000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>2828000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>2723000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>2722000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>2714000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>2731000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>2615000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>2654000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>2678000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>2702000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>2658000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>2618000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>2551000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>2706000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>2469000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9206,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9331,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9456,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9581,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9706,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14972000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4738000</v>
+      </c>
+      <c r="F89" s="3">
         <v>14113000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>9100000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>12941000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5411000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>13525000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>6561000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>12108000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>4249000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>16712000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>813000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>13568000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>4633000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>13143000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>6458000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>12998000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-3758000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>7890000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>3868000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>9565000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>4706000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>13194000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>3924000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>11939000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>7017000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>10716000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>3354000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>7622000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>3563000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>10445000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>6213000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>5934000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>5161000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>11277000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>5700000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>5975000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>5385000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>11892000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>4850000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,127 +9880,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7497000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-6684000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-8015000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-7218000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-6423000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-4986000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-7087000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-6189000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-5831000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-4676000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-5932000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-5458000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4787000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-4429000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-4796000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-4569000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-3953000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-3539000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-4518000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-3569000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-2805000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2214000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-3826000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-2869000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-1817000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-1752000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-2894000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-2666000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-2205000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-3330000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-2732000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-2464000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-1818000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-3143000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-2485000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-2433000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-3980000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-6320000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-10299000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +10126,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10251,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7527000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-6737000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-7320000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-7831000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-6106000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-5093000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-8718000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2533000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-5719000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4409000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-5913000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-5465000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-5049000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-4860000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-4757000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-4381000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-4026000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-4558000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-4485000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-3932000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-3448000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>5850000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-3564000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-2873000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1938000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1696000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-2843000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-2461000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-2689000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-1135000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-3482000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-16126000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-2746000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-1682000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-3206000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-2312000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-1681000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-1861000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-2937000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-6634000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,127 +10425,135 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1973000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1972000</v>
+      </c>
+      <c r="F96" s="3">
         <v>1877000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1875000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>1875000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1880000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>1684000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1668000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>1665000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>1671000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>1534000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>1534000</v>
       </c>
       <c r="N96" s="3">
         <v>1534000</v>
       </c>
       <c r="O96" s="3">
+        <v>1534000</v>
+      </c>
+      <c r="P96" s="3">
+        <v>1534000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>1538000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-1514000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-1519000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-1538000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-1543000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-1525000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-1536000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-1542000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-1549000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-1534000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-1524000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-1503000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-1509000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-1516000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-1520000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-1505000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-1530000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-1534000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-1533000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-1510000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-1526000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-1539000</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-1549000</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-1534000</v>
       </c>
       <c r="AO96" s="3">
         <v>-1549000</v>
       </c>
+      <c r="AP96" s="3">
+        <v>-1534000</v>
+      </c>
+      <c r="AQ96" s="3">
+        <v>-1549000</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10671,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10796,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,361 +10921,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7170000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2328000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-6541000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-19000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-7001000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>8000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-5149000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2728000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-6624000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-321000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-13235000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>3130000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-5249000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1940000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-11458000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-4181000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-6715000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>5315000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-4715000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-6554000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-6160000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-5399000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-4777000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-3526000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-8379000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>565000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-7086000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1682000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-4685000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-846000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-8458000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>3441000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>4966000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-2486000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-8459000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-2785000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-4659000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-3972000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-7794000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>70000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-290000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-11000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-346000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>76000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-154000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-7000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>154000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>258000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-231000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-149000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>49000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>258000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-231000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-149000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>49000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-22000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-97000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>30000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-51000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>405000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-101000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>346000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-415000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>97000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>100000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-220000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-46000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>47000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-186000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-442000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>143000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>101000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-46000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>293000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>139000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>-227000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AQ101" s="3">
         <v>105000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>673000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F102" s="3">
         <v>224000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1220000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-55000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>396000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-632000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1289000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-581000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-475000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2360000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1676000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>3263000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1867000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2814000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-2335000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2108000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2952000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1332000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-6715000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-13000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>5106000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>5258000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-2576000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>1968000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>5471000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>884000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-689000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>28000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>1536000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-1448000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-6658000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>7712000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>1136000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-287000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>557000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-72000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-309000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>928000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>-1737000</v>
       </c>
     </row>
